--- a/Wochenplan/Wochenuebersicht_20260520.xlsx
+++ b/Wochenplan/Wochenuebersicht_20260520.xlsx
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,11 +76,6 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -100,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -145,9 +140,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -891,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -985,9 +977,18 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>DONNERSTAG</t>
+      <c r="A7" s="14" t="inlineStr"/>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Lauch-Speck Quiche</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Charge 1/1</t>
         </is>
       </c>
     </row>
@@ -995,7 +996,7 @@
       <c r="A8" s="14" t="inlineStr"/>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Donauwelle</t>
+          <t>Kaese-Rhabarber Schnitte</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
@@ -1008,25 +1009,25 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="14" t="inlineStr"/>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Mango-Passionsfrucht Tartelette</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>60 Stueck</t>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>DONNERSTAG</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>FREITAG</t>
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Kaesekuchen</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Charge 3/4</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1043,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Charge 3/4</t>
+          <t>Charge 4/4</t>
         </is>
       </c>
     </row>
@@ -1050,15 +1051,15 @@
       <c r="A12" s="14" t="inlineStr"/>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Kaesekuchen</t>
+          <t>Donauwelle</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Charge 4/4</t>
+          <t>Charge 1/1</t>
         </is>
       </c>
     </row>
@@ -1066,40 +1067,23 @@
       <c r="A13" s="14" t="inlineStr"/>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Lauch-Speck Quiche</t>
+          <t>Mango-Passionsfrucht Tartelette</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="14" t="inlineStr"/>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Kaese-Rhabarber Schnitte</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Charge 1/1</t>
+          <t>60 Stueck</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Wochenplan/Wochenuebersicht_20260520.xlsx
+++ b/Wochenplan/Wochenuebersicht_20260520.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Produktionsbedarf" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Wochenplan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produktionsbedarf" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wochenplan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -95,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -140,6 +145,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -613,13 +621,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>0</v>
@@ -641,13 +649,13 @@
         <v>11</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>0</v>
@@ -669,13 +677,13 @@
         <v>9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>0</v>
@@ -725,20 +733,20 @@
         <v>18</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Beide unter Schwelle - Mango (31.0&lt;45)</t>
+          <t>Beeren unter Schwelle (32.0&lt;45)</t>
         </is>
       </c>
     </row>
@@ -758,20 +766,20 @@
         <v>18</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Beide unter Schwelle - Mango (31.0&lt;45)</t>
+          <t>Beeren unter Schwelle (32.0&lt;45)</t>
         </is>
       </c>
     </row>
@@ -791,7 +799,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
@@ -806,7 +814,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Lager OK (40&gt;=30)</t>
+          <t>Lager OK (50&gt;=30)</t>
         </is>
       </c>
     </row>
@@ -824,11 +832,11 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6240g</t>
+          <t>7800g</t>
         </is>
       </c>
     </row>
@@ -840,7 +848,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>12x/2400g</t>
+          <t>18x/3600g</t>
         </is>
       </c>
     </row>
@@ -852,7 +860,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>8x/1440g</t>
+          <t>10x/1800g</t>
         </is>
       </c>
     </row>
@@ -883,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -940,7 +948,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/4</t>
+          <t>Charge 1/5</t>
         </is>
       </c>
     </row>
@@ -956,7 +964,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Charge 2/4</t>
+          <t>Charge 2/5</t>
         </is>
       </c>
     </row>
@@ -972,7 +980,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/1</t>
+          <t>Charge 1/2</t>
         </is>
       </c>
     </row>
@@ -984,11 +992,11 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/1</t>
+          <t>Charge 1/2</t>
         </is>
       </c>
     </row>
@@ -1004,30 +1012,30 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/1</t>
+          <t>Charge 1/2</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Beeren Tartelette</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>60 Stueck</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>DONNERSTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Kaesekuchen</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Charge 3/4</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1051,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Charge 4/4</t>
+          <t>Charge 3/5</t>
         </is>
       </c>
     </row>
@@ -1051,15 +1059,15 @@
       <c r="A12" s="14" t="inlineStr"/>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Donauwelle</t>
+          <t>Kaesekuchen</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Charge 1/1</t>
+          <t>Charge 4/5</t>
         </is>
       </c>
     </row>
@@ -1067,23 +1075,95 @@
       <c r="A13" s="14" t="inlineStr"/>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Mango-Passionsfrucht Tartelette</t>
+          <t>Lauch-Speck Quiche</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>60 Stueck</t>
+          <t>Charge 2/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="14" t="inlineStr"/>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Donauwelle</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Charge 1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>FREITAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="14" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Kaesekuchen</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Charge 5/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="14" t="inlineStr"/>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Bienenstich</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Charge 2/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="14" t="inlineStr"/>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Kaese-Rhabarber Schnitte</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Charge 2/2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
